--- a/examples/09_ZrO2_on_fused_silica_1mm_backside_65deg.xlsx
+++ b/examples/09_ZrO2_on_fused_silica_1mm_backside_65deg.xlsx
@@ -478,10 +478,10 @@
         <v>400</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>15.637</v>
+        <v>15.6366</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>355.0605</v>
+        <v>355.0431</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.035</v>
@@ -495,10 +495,10 @@
         <v>402</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>15.6482</v>
+        <v>15.6479</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8.126300000000001</v>
+        <v>8.1488</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0347</v>
@@ -512,10 +512,10 @@
         <v>404</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>15.3742</v>
+        <v>15.3724</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>21.8692</v>
+        <v>21.9282</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.0344</v>
@@ -529,10 +529,10 @@
         <v>406</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>14.8143</v>
+        <v>14.8119</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>38.4245</v>
+        <v>38.5077</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0341</v>
@@ -546,10 +546,10 @@
         <v>408</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>14.3356</v>
+        <v>14.3336</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>57.4072</v>
+        <v>57.4934</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0337</v>
@@ -563,10 +563,10 @@
         <v>410</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>13.9572</v>
+        <v>13.9558</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>76.6705</v>
+        <v>76.74209999999999</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0334</v>
@@ -580,10 +580,10 @@
         <v>412</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>13.675</v>
+        <v>13.6743</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>94.7915</v>
+        <v>94.8437</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0331</v>
@@ -597,16 +597,16 @@
         <v>414</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>13.431</v>
+        <v>13.4306</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>111.535</v>
+        <v>111.5708</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0328</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1594</v>
+        <v>0.1595</v>
       </c>
     </row>
     <row r="10">
@@ -614,10 +614,10 @@
         <v>416</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>13.2066</v>
+        <v>13.2064</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>126.565</v>
+        <v>126.5888</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0325</v>
@@ -631,10 +631,10 @@
         <v>418</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.2259</v>
+        <v>13.2257</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>140.2525</v>
+        <v>140.2678</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0322</v>
@@ -648,10 +648,10 @@
         <v>420</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>13.1162</v>
+        <v>13.1161</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>153.2029</v>
+        <v>153.2118</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0319</v>
@@ -668,7 +668,7 @@
         <v>12.9982</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>165.7106</v>
+        <v>165.7142</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0316</v>
@@ -685,7 +685,7 @@
         <v>12.9699</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>178.4792</v>
+        <v>178.4783</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0313</v>
@@ -702,7 +702,7 @@
         <v>12.9109</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>190.8978</v>
+        <v>190.8924</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.0311</v>
@@ -719,7 +719,7 @@
         <v>12.8615</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>203.7535</v>
+        <v>203.7433</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0308</v>
@@ -736,7 +736,7 @@
         <v>12.8009</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>217.1383</v>
+        <v>217.1224</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0305</v>
@@ -750,10 +750,10 @@
         <v>432</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12.8418</v>
+        <v>12.8417</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>230.8595</v>
+        <v>230.8366</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.0302</v>
@@ -767,10 +767,10 @@
         <v>434</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>12.8846</v>
+        <v>12.8844</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>245.873</v>
+        <v>245.8416</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0299</v>
@@ -784,10 +784,10 @@
         <v>436</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>13.0324</v>
+        <v>13.032</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>262.0922</v>
+        <v>262.0507</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.0297</v>
@@ -801,10 +801,10 @@
         <v>438</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>13.3002</v>
+        <v>13.2993</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>279.0123</v>
+        <v>278.9608</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.0294</v>
@@ -818,10 +818,10 @@
         <v>440</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>13.6559</v>
+        <v>13.6546</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>295.5254</v>
+        <v>295.4674</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0291</v>
@@ -835,10 +835,10 @@
         <v>442</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>14.0785</v>
+        <v>14.0767</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>311.9619</v>
+        <v>311.9043</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0288</v>
@@ -852,10 +852,10 @@
         <v>444</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>14.5993</v>
+        <v>14.5974</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>326.6628</v>
+        <v>326.6136</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.0286</v>
@@ -869,10 +869,10 @@
         <v>446</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>15.0703</v>
+        <v>15.0687</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>338.8024</v>
+        <v>338.7673</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0283</v>
@@ -886,10 +886,10 @@
         <v>448</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>15.5561</v>
+        <v>15.5554</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>349.3171</v>
+        <v>349.2983</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0281</v>
@@ -906,7 +906,7 @@
         <v>15.8057</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>358.8728</v>
+        <v>358.8702</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.0278</v>
@@ -920,10 +920,10 @@
         <v>452</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>15.7583</v>
+        <v>15.758</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8.2674</v>
+        <v>8.2803</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0275</v>
@@ -937,10 +937,10 @@
         <v>454</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>15.5184</v>
+        <v>15.5175</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>18.2266</v>
+        <v>18.2539</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0273</v>
@@ -954,10 +954,10 @@
         <v>456</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>15.1796</v>
+        <v>15.1782</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>29.4896</v>
+        <v>29.5284</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.027</v>
@@ -971,10 +971,10 @@
         <v>458</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>14.7119</v>
+        <v>14.7104</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42.0297</v>
+        <v>42.0746</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0268</v>
@@ -988,10 +988,10 @@
         <v>460</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>14.2525</v>
+        <v>14.2512</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>55.4065</v>
+        <v>55.4515</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0266</v>
@@ -1005,10 +1005,10 @@
         <v>462</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>13.9186</v>
+        <v>13.9176</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>69.3777</v>
+        <v>69.4181</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.0263</v>
@@ -1022,10 +1022,10 @@
         <v>464</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>13.621</v>
+        <v>13.6203</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>83.23869999999999</v>
+        <v>83.2722</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0261</v>
@@ -1039,10 +1039,10 @@
         <v>466</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>13.4047</v>
+        <v>13.4042</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>96.4178</v>
+        <v>96.44410000000001</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0258</v>
@@ -1056,10 +1056,10 @@
         <v>468</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>13.1573</v>
+        <v>13.157</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>108.6926</v>
+        <v>108.7127</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0256</v>
@@ -1073,10 +1073,10 @@
         <v>470</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>13.0365</v>
+        <v>13.0363</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>120.3047</v>
+        <v>120.3197</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0254</v>
@@ -1090,10 +1090,10 @@
         <v>472</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>12.8721</v>
+        <v>12.872</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>131.2455</v>
+        <v>131.2565</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.0251</v>
@@ -1107,10 +1107,10 @@
         <v>474</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>12.7979</v>
+        <v>12.7978</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>141.7932</v>
+        <v>141.801</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0249</v>
@@ -1127,7 +1127,7 @@
         <v>12.6677</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>152.0797</v>
+        <v>152.0848</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0247</v>
@@ -1144,7 +1144,7 @@
         <v>12.6452</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>161.9529</v>
+        <v>161.9558</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0245</v>
@@ -1161,7 +1161,7 @@
         <v>12.5503</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>171.5375</v>
+        <v>171.5384</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0242</v>
@@ -1178,7 +1178,7 @@
         <v>12.5333</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>181.3984</v>
+        <v>181.3974</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.024</v>
@@ -1195,7 +1195,7 @@
         <v>12.4761</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>191.1551</v>
+        <v>191.1522</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0238</v>
@@ -1212,7 +1212,7 @@
         <v>12.421</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>200.8197</v>
+        <v>200.8149</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0236</v>
@@ -1229,7 +1229,7 @@
         <v>12.4865</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>211.0636</v>
+        <v>211.0566</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0234</v>
@@ -1243,10 +1243,10 @@
         <v>490</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>12.4763</v>
+        <v>12.4762</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>221.554</v>
+        <v>221.5446</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0232</v>
@@ -1260,10 +1260,10 @@
         <v>492</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>12.535</v>
+        <v>12.5349</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>232.1667</v>
+        <v>232.1545</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.023</v>
@@ -1277,10 +1277,10 @@
         <v>494</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>12.6072</v>
+        <v>12.6071</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>243.2525</v>
+        <v>243.2373</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0228</v>
@@ -1294,10 +1294,10 @@
         <v>496</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>12.7256</v>
+        <v>12.7254</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>254.7431</v>
+        <v>254.7244</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0226</v>
@@ -1311,10 +1311,10 @@
         <v>498</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>12.9249</v>
+        <v>12.9245</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>266.6771</v>
+        <v>266.6548</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0224</v>
@@ -1328,10 +1328,10 @@
         <v>500</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>13.1358</v>
+        <v>13.1353</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>278.6299</v>
+        <v>278.6043</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0222</v>
@@ -1345,10 +1345,10 @@
         <v>502</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>13.3911</v>
+        <v>13.3904</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>291.0532</v>
+        <v>291.0251</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.022</v>
@@ -1362,10 +1362,10 @@
         <v>504</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13.7211</v>
+        <v>13.7202</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>302.8023</v>
+        <v>302.7731</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0218</v>
@@ -1379,10 +1379,10 @@
         <v>506</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>14.0828</v>
+        <v>14.0817</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>313.701</v>
+        <v>313.6726</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.0216</v>
@@ -1396,10 +1396,10 @@
         <v>508</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>14.5053</v>
+        <v>14.5042</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>324.0086</v>
+        <v>323.9829</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0215</v>
@@ -1413,10 +1413,10 @@
         <v>510</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>14.9154</v>
+        <v>14.9144</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>333.1877</v>
+        <v>333.1663</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0213</v>
@@ -1430,10 +1430,10 @@
         <v>512</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>15.3272</v>
+        <v>15.3264</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>341.2543</v>
+        <v>341.2383</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0211</v>
@@ -1447,10 +1447,10 @@
         <v>514</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>15.6086</v>
+        <v>15.6082</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>348.7204</v>
+        <v>348.7102</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0209</v>
@@ -1464,10 +1464,10 @@
         <v>516</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>15.8519</v>
+        <v>15.8518</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>355.3867</v>
+        <v>355.3823</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0207</v>
@@ -1484,7 +1484,7 @@
         <v>15.9248</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>1.9959</v>
+        <v>1.9972</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.0206</v>
@@ -1498,10 +1498,10 @@
         <v>520</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>15.9082</v>
+        <v>15.9081</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>8.4239</v>
+        <v>8.4306</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0204</v>
@@ -1515,10 +1515,10 @@
         <v>522</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>15.6658</v>
+        <v>15.6654</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>15.1439</v>
+        <v>15.1556</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0202</v>
@@ -1532,10 +1532,10 @@
         <v>524</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>15.4098</v>
+        <v>15.4092</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>22.484</v>
+        <v>22.5001</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0201</v>
@@ -1549,10 +1549,10 @@
         <v>526</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>15.0585</v>
+        <v>15.0577</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>30.5905</v>
+        <v>30.61</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0199</v>
@@ -1566,10 +1566,10 @@
         <v>528</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>14.7284</v>
+        <v>14.7276</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>39.1053</v>
+        <v>39.1269</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0198</v>
@@ -1583,10 +1583,10 @@
         <v>530</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>14.3832</v>
+        <v>14.3824</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>48.3588</v>
+        <v>48.381</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0196</v>
@@ -1600,10 +1600,10 @@
         <v>532</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>14.0655</v>
+        <v>14.0648</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>57.7756</v>
+        <v>57.797</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.0195</v>
@@ -1617,10 +1617,10 @@
         <v>534</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>13.7721</v>
+        <v>13.7715</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>67.4991</v>
+        <v>67.5189</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0193</v>
@@ -1634,10 +1634,10 @@
         <v>536</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>13.578</v>
+        <v>13.5776</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>77.22329999999999</v>
+        <v>77.24079999999999</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0192</v>
@@ -1651,10 +1651,10 @@
         <v>538</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>13.334</v>
+        <v>13.3336</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>86.6901</v>
+        <v>86.7051</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.019</v>
@@ -1668,10 +1668,10 @@
         <v>540</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13.1237</v>
+        <v>13.1234</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>95.7586</v>
+        <v>95.7713</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0189</v>
@@ -1685,10 +1685,10 @@
         <v>542</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>12.9562</v>
+        <v>12.956</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>104.6166</v>
+        <v>104.6272</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.0187</v>
@@ -1702,10 +1702,10 @@
         <v>544</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>12.8198</v>
+        <v>12.8196</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>113.3178</v>
+        <v>113.3265</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0186</v>
@@ -1719,10 +1719,10 @@
         <v>546</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>12.6879</v>
+        <v>12.6878</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>121.675</v>
+        <v>121.6821</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0185</v>
@@ -1736,10 +1736,10 @@
         <v>548</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>12.5962</v>
+        <v>12.5961</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>129.8225</v>
+        <v>129.8282</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0183</v>
@@ -1756,7 +1756,7 @@
         <v>12.522</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>137.4799</v>
+        <v>137.4844</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.0182</v>
@@ -1773,7 +1773,7 @@
         <v>12.4083</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>145.1445</v>
+        <v>145.148</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.0181</v>
@@ -1790,7 +1790,7 @@
         <v>12.3485</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>152.8062</v>
+        <v>152.8087</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0179</v>
@@ -1804,10 +1804,10 @@
         <v>556</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>12.3043</v>
+        <v>12.3042</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>160.1659</v>
+        <v>160.1675</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0178</v>
@@ -1824,7 +1824,7 @@
         <v>12.2141</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>167.3366</v>
+        <v>167.3375</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0177</v>
@@ -1841,7 +1841,7 @@
         <v>12.2091</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>174.6435</v>
+        <v>174.6436</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0176</v>
@@ -1858,7 +1858,7 @@
         <v>12.2002</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>181.9326</v>
+        <v>181.9321</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0175</v>
@@ -1875,7 +1875,7 @@
         <v>12.1577</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>188.9854</v>
+        <v>188.9842</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0174</v>
@@ -1892,7 +1892,7 @@
         <v>12.1454</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>196.5621</v>
+        <v>196.5602</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0173</v>
@@ -1909,7 +1909,7 @@
         <v>12.1619</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>203.8711</v>
+        <v>203.8685</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0172</v>
@@ -1926,7 +1926,7 @@
         <v>12.1468</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>211.1849</v>
+        <v>211.1815</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.017</v>
@@ -1940,10 +1940,10 @@
         <v>572</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>12.2228</v>
+        <v>12.2227</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>218.7856</v>
+        <v>218.7814</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0169</v>
@@ -1960,7 +1960,7 @@
         <v>12.2889</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>226.4514</v>
+        <v>226.4464</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.0168</v>
@@ -1974,10 +1974,10 @@
         <v>576</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>12.3152</v>
+        <v>12.3151</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>234.2058</v>
+        <v>234.1998</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0168</v>
@@ -1991,10 +1991,10 @@
         <v>578</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>12.3937</v>
+        <v>12.3936</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>242.362</v>
+        <v>242.3551</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0167</v>
@@ -2008,10 +2008,10 @@
         <v>580</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>12.4793</v>
+        <v>12.4792</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>250.2761</v>
+        <v>250.2681</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0166</v>
@@ -2025,16 +2025,16 @@
         <v>582</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>12.6414</v>
+        <v>12.6412</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>258.2756</v>
+        <v>258.2665</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0165</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="94">
@@ -2042,10 +2042,10 @@
         <v>584</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>12.7823</v>
+        <v>12.7821</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>266.6643</v>
+        <v>266.6542</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0164</v>
@@ -2059,10 +2059,10 @@
         <v>586</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>12.9351</v>
+        <v>12.9348</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>274.851</v>
+        <v>274.8399</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0163</v>
@@ -2076,10 +2076,10 @@
         <v>588</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>13.1019</v>
+        <v>13.1016</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>283.0844</v>
+        <v>283.0723</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.0162</v>
@@ -2093,10 +2093,10 @@
         <v>590</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>13.3303</v>
+        <v>13.3299</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>291.1252</v>
+        <v>291.1125</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0162</v>
@@ -2110,10 +2110,10 @@
         <v>592</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13.6011</v>
+        <v>13.6007</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>299.2296</v>
+        <v>299.2164</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0161</v>
@@ -2127,10 +2127,10 @@
         <v>594</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>13.8171</v>
+        <v>13.8166</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>307.0716</v>
+        <v>307.0584</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.016</v>
@@ -2144,10 +2144,10 @@
         <v>596</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>14.0928</v>
+        <v>14.0923</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>314.2407</v>
+        <v>314.2278</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0159</v>
@@ -2161,10 +2161,10 @@
         <v>598</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>14.4034</v>
+        <v>14.4028</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>321.1166</v>
+        <v>321.1044</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0159</v>
@@ -2178,10 +2178,10 @@
         <v>600</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>14.7027</v>
+        <v>14.7022</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>327.5494</v>
+        <v>327.5383</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0158</v>
@@ -2195,10 +2195,10 @@
         <v>602</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>14.9644</v>
+        <v>14.9639</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>333.4956</v>
+        <v>333.486</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0157</v>
@@ -2212,10 +2212,10 @@
         <v>604</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>15.2859</v>
+        <v>15.2854</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>339.1054</v>
+        <v>339.0973</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.0157</v>
@@ -2229,10 +2229,10 @@
         <v>606</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>15.5437</v>
+        <v>15.5434</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>344.2455</v>
+        <v>344.2392</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0156</v>
@@ -2246,10 +2246,10 @@
         <v>608</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>15.7556</v>
+        <v>15.7554</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>348.9238</v>
+        <v>348.9192</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0156</v>
@@ -2263,10 +2263,10 @@
         <v>610</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>15.9044</v>
+        <v>15.9043</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>353.4357</v>
+        <v>353.4329</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0155</v>
@@ -2283,7 +2283,7 @@
         <v>16.0145</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>357.857</v>
+        <v>357.856</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0155</v>
@@ -2300,7 +2300,7 @@
         <v>16.058</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>2.1923</v>
+        <v>2.193</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0154</v>
@@ -2314,10 +2314,10 @@
         <v>616</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>16.0139</v>
+        <v>16.0138</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>6.4513</v>
+        <v>6.4537</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0154</v>
@@ -2331,10 +2331,10 @@
         <v>618</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>15.8779</v>
+        <v>15.8778</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>10.8649</v>
+        <v>10.8688</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.0153</v>
@@ -2348,10 +2348,10 @@
         <v>620</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>15.7398</v>
+        <v>15.7396</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>15.591</v>
+        <v>15.5963</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.0153</v>
@@ -2365,10 +2365,10 @@
         <v>622</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>15.5299</v>
+        <v>15.5296</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>20.3295</v>
+        <v>20.3362</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.0153</v>
@@ -2382,10 +2382,10 @@
         <v>624</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>15.3226</v>
+        <v>15.3222</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>25.2602</v>
+        <v>25.268</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.0152</v>
@@ -2399,10 +2399,10 @@
         <v>626</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>15.0545</v>
+        <v>15.0541</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>30.6167</v>
+        <v>30.6254</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.0152</v>
@@ -2416,10 +2416,10 @@
         <v>628</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>14.8052</v>
+        <v>14.8048</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>36.2003</v>
+        <v>36.2096</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.0152</v>
@@ -2433,10 +2433,10 @@
         <v>630</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>14.5621</v>
+        <v>14.5617</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>41.9855</v>
+        <v>41.995</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.0151</v>
@@ -2450,10 +2450,10 @@
         <v>632</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>14.2939</v>
+        <v>14.2935</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>48.2267</v>
+        <v>48.2364</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.0151</v>
@@ -2467,10 +2467,10 @@
         <v>634</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>14.0811</v>
+        <v>14.0807</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>54.3441</v>
+        <v>54.3535</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.0151</v>
@@ -2484,10 +2484,10 @@
         <v>636</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13.8435</v>
+        <v>13.8432</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>60.7817</v>
+        <v>60.7907</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.0151</v>
@@ -2501,10 +2501,10 @@
         <v>638</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>13.6599</v>
+        <v>13.6596</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>67.1559</v>
+        <v>67.1644</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.015</v>
@@ -2518,10 +2518,10 @@
         <v>640</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13.4808</v>
+        <v>13.4806</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>73.3434</v>
+        <v>73.35129999999999</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.015</v>
@@ -2535,10 +2535,10 @@
         <v>642</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13.3083</v>
+        <v>13.3081</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>79.81740000000001</v>
+        <v>79.8246</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.015</v>
@@ -2552,10 +2552,10 @@
         <v>644</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>13.1015</v>
+        <v>13.1013</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>86.2187</v>
+        <v>86.2252</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.015</v>
@@ -2569,10 +2569,10 @@
         <v>646</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>12.9842</v>
+        <v>12.9841</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>92.1832</v>
+        <v>92.1891</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.015</v>
@@ -2586,10 +2586,10 @@
         <v>648</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>12.8267</v>
+        <v>12.8266</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>98.3126</v>
+        <v>98.31789999999999</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.015</v>
@@ -2603,10 +2603,10 @@
         <v>650</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>12.7438</v>
+        <v>12.7437</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>104.2826</v>
+        <v>104.2872</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.015</v>
@@ -2620,16 +2620,16 @@
         <v>652</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>12.6206</v>
+        <v>12.6205</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>110.088</v>
+        <v>110.0921</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.0774</v>
+        <v>0.0775</v>
       </c>
     </row>
     <row r="129">
@@ -2640,7 +2640,7 @@
         <v>12.5296</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>115.8487</v>
+        <v>115.8523</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.015</v>
@@ -2654,10 +2654,10 @@
         <v>656</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>12.4559</v>
+        <v>12.4558</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>121.6282</v>
+        <v>121.6313</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.015</v>
@@ -2671,10 +2671,10 @@
         <v>658</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>12.3489</v>
+        <v>12.3488</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>127.0471</v>
+        <v>127.0498</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.015</v>
@@ -2688,10 +2688,10 @@
         <v>660</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>12.2892</v>
+        <v>12.2891</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>132.5915</v>
+        <v>132.5938</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.015</v>
@@ -2708,7 +2708,7 @@
         <v>12.204</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>137.9102</v>
+        <v>137.9121</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.015</v>
@@ -2725,7 +2725,7 @@
         <v>12.1609</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>143.1784</v>
+        <v>143.1801</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.015</v>
@@ -2742,7 +2742,7 @@
         <v>12.1383</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>148.3829</v>
+        <v>148.3843</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.015</v>
@@ -2759,7 +2759,7 @@
         <v>12.0477</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>153.6922</v>
+        <v>153.6933</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.015</v>
@@ -2776,7 +2776,7 @@
         <v>11.991</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>158.9501</v>
+        <v>158.9509</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.015</v>
@@ -2793,7 +2793,7 @@
         <v>11.9628</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>163.9352</v>
+        <v>163.9357</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.015</v>
@@ -2810,7 +2810,7 @@
         <v>11.9639</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>169.0221</v>
+        <v>169.0224</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.015</v>
@@ -2827,7 +2827,7 @@
         <v>11.9391</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>174.1856</v>
+        <v>174.1858</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.015</v>
@@ -2844,7 +2844,7 @@
         <v>11.9034</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>179.2593</v>
+        <v>179.2592</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.015</v>
@@ -2858,10 +2858,10 @@
         <v>680</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>11.9041</v>
+        <v>11.9042</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>184.1481</v>
+        <v>184.1478</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.015</v>
@@ -2878,7 +2878,7 @@
         <v>11.871</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>189.332</v>
+        <v>189.3315</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.015</v>
@@ -2895,7 +2895,7 @@
         <v>11.8901</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>194.4237</v>
+        <v>194.423</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.015</v>
@@ -2912,7 +2912,7 @@
         <v>11.9126</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>199.3252</v>
+        <v>199.3242</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.015</v>
@@ -2929,7 +2929,7 @@
         <v>11.9162</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>204.4739</v>
+        <v>204.4728</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
@@ -2946,7 +2946,7 @@
         <v>11.9761</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>209.5902</v>
+        <v>209.5888</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
@@ -2963,7 +2963,7 @@
         <v>11.996</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>214.7954</v>
+        <v>214.7938</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
@@ -2980,7 +2980,7 @@
         <v>11.9994</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>219.896</v>
+        <v>219.8942</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
@@ -2994,10 +2994,10 @@
         <v>696</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>12.021</v>
+        <v>12.0209</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>225.0787</v>
+        <v>225.0767</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
@@ -3011,10 +3011,10 @@
         <v>698</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>12.0684</v>
+        <v>12.0683</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>230.1269</v>
+        <v>230.1246</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
@@ -3031,7 +3031,7 @@
         <v>12.1313</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>235.2663</v>
+        <v>235.2638</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
@@ -3048,7 +3048,7 @@
         <v>12.1826</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>240.4232</v>
+        <v>240.4205</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
@@ -3065,7 +3065,7 @@
         <v>12.2839</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>245.8583</v>
+        <v>245.8552</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
@@ -3079,10 +3079,10 @@
         <v>706</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>12.3302</v>
+        <v>12.3301</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>251.1401</v>
+        <v>251.1368</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
@@ -3096,10 +3096,10 @@
         <v>708</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>12.4273</v>
+        <v>12.4272</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>256.4807</v>
+        <v>256.4772</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
@@ -3113,10 +3113,10 @@
         <v>710</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>12.5307</v>
+        <v>12.5306</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>261.7577</v>
+        <v>261.7538</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
@@ -3130,10 +3130,10 @@
         <v>712</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>12.6373</v>
+        <v>12.6372</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>267.1235</v>
+        <v>267.1195</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
@@ -3147,10 +3147,10 @@
         <v>714</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>12.7603</v>
+        <v>12.7602</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>272.3843</v>
+        <v>272.38</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
@@ -3164,10 +3164,10 @@
         <v>716</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>12.8721</v>
+        <v>12.872</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>277.7359</v>
+        <v>277.7313</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
@@ -3181,10 +3181,10 @@
         <v>718</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>12.9949</v>
+        <v>12.9948</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>282.836</v>
+        <v>282.8313</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0.015</v>
@@ -3198,10 +3198,10 @@
         <v>720</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>13.1665</v>
+        <v>13.1663</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>288.1282</v>
+        <v>288.1233</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
@@ -3215,10 +3215,10 @@
         <v>722</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13.3334</v>
+        <v>13.3332</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>293.1943</v>
+        <v>293.1893</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
@@ -3232,10 +3232,10 @@
         <v>724</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>13.4683</v>
+        <v>13.4681</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>298.1421</v>
+        <v>298.1369</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
@@ -3249,10 +3249,10 @@
         <v>726</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>13.6212</v>
+        <v>13.621</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>302.9808</v>
+        <v>302.9756</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
@@ -3266,10 +3266,10 @@
         <v>728</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>13.8199</v>
+        <v>13.8197</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>307.7392</v>
+        <v>307.734</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0.015</v>
@@ -3283,10 +3283,10 @@
         <v>730</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>13.9969</v>
+        <v>13.9967</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>312.2001</v>
+        <v>312.195</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
@@ -3300,10 +3300,10 @@
         <v>732</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>14.199</v>
+        <v>14.1987</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>316.6523</v>
+        <v>316.6473</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
@@ -3317,10 +3317,10 @@
         <v>734</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>14.3986</v>
+        <v>14.3984</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>321</v>
+        <v>320.9952</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
@@ -3334,10 +3334,10 @@
         <v>736</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>14.5833</v>
+        <v>14.583</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>325.1708</v>
+        <v>325.1663</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
@@ -3351,10 +3351,10 @@
         <v>738</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>14.801</v>
+        <v>14.8008</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>328.8845</v>
+        <v>328.8802</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
@@ -3368,10 +3368,10 @@
         <v>740</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>15.0398</v>
+        <v>15.0396</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>332.5596</v>
+        <v>332.5557</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
@@ -3385,10 +3385,10 @@
         <v>742</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>15.1959</v>
+        <v>15.1957</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>336.1376</v>
+        <v>336.1341</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
@@ -3402,10 +3402,10 @@
         <v>744</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>15.3841</v>
+        <v>15.3839</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>339.5762</v>
+        <v>339.5731</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
@@ -3419,10 +3419,10 @@
         <v>746</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>15.56</v>
+        <v>15.5598</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>342.6527</v>
+        <v>342.65</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
@@ -3436,10 +3436,10 @@
         <v>748</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>15.6798</v>
+        <v>15.6797</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>345.7822</v>
+        <v>345.7799</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
@@ -3453,10 +3453,10 @@
         <v>750</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>15.8415</v>
+        <v>15.8414</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>348.8124</v>
+        <v>348.8106</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
@@ -3470,10 +3470,10 @@
         <v>752</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>15.9584</v>
+        <v>15.9583</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>351.5987</v>
+        <v>351.5973</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
@@ -3487,10 +3487,10 @@
         <v>754</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>16.0742</v>
+        <v>16.0741</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>354.3319</v>
+        <v>354.331</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
@@ -3507,7 +3507,7 @@
         <v>16.1</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>357.0157</v>
+        <v>357.0151</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
@@ -3524,7 +3524,7 @@
         <v>16.1573</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>359.7281</v>
+        <v>359.728</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
@@ -3541,7 +3541,7 @@
         <v>16.1398</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>2.4543</v>
+        <v>2.4546</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
@@ -3558,7 +3558,7 @@
         <v>16.1038</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>5.1041</v>
+        <v>5.1048</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
@@ -3572,10 +3572,10 @@
         <v>764</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>16.087</v>
+        <v>16.0869</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>7.7755</v>
+        <v>7.7766</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
@@ -3589,10 +3589,10 @@
         <v>766</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>16.0272</v>
+        <v>16.0271</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>10.5635</v>
+        <v>10.5649</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
@@ -3609,7 +3609,7 @@
         <v>15.9053</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>13.3227</v>
+        <v>13.3246</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
@@ -3623,10 +3623,10 @@
         <v>770</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>15.7888</v>
+        <v>15.7887</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>16.2253</v>
+        <v>16.2275</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
@@ -3640,10 +3640,10 @@
         <v>772</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>15.6426</v>
+        <v>15.6425</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>19.0982</v>
+        <v>19.1007</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
@@ -3657,10 +3657,10 @@
         <v>774</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>15.5133</v>
+        <v>15.5132</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>22.0334</v>
+        <v>22.0361</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
@@ -3674,10 +3674,10 @@
         <v>776</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>15.3494</v>
+        <v>15.3492</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>25.0748</v>
+        <v>25.0778</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
@@ -3691,10 +3691,10 @@
         <v>778</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>15.1517</v>
+        <v>15.1515</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>28.5639</v>
+        <v>28.567</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
@@ -3708,10 +3708,10 @@
         <v>780</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>14.9879</v>
+        <v>14.9877</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>31.6309</v>
+        <v>31.6343</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
@@ -3725,10 +3725,10 @@
         <v>782</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>14.8457</v>
+        <v>14.8455</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>35.0784</v>
+        <v>35.0818</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0.015</v>
@@ -3742,10 +3742,10 @@
         <v>784</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>14.6476</v>
+        <v>14.6474</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>38.5567</v>
+        <v>38.5602</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0.015</v>
@@ -3759,10 +3759,10 @@
         <v>786</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>14.5206</v>
+        <v>14.5204</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>42.2455</v>
+        <v>42.2491</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0.015</v>
@@ -3776,10 +3776,10 @@
         <v>788</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>14.3751</v>
+        <v>14.375</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>45.7524</v>
+        <v>45.756</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0.015</v>
@@ -3793,10 +3793,10 @@
         <v>790</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>14.2044</v>
+        <v>14.2042</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>49.4234</v>
+        <v>49.427</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0.015</v>
@@ -3810,10 +3810,10 @@
         <v>792</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>14.0458</v>
+        <v>14.0457</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>53.325</v>
+        <v>53.3285</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0.015</v>
@@ -3827,10 +3827,10 @@
         <v>794</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>13.9176</v>
+        <v>13.9175</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>57.0048</v>
+        <v>57.0082</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0.015</v>
@@ -3844,10 +3844,10 @@
         <v>796</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>13.7536</v>
+        <v>13.7535</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>60.8472</v>
+        <v>60.8505</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>0.015</v>
@@ -3861,10 +3861,10 @@
         <v>798</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>13.635</v>
+        <v>13.6349</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>64.7786</v>
+        <v>64.7818</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0.015</v>
@@ -3878,10 +3878,10 @@
         <v>800</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>13.4412</v>
+        <v>13.4411</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>68.7034</v>
+        <v>68.70650000000001</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0.015</v>
